--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -11210,22 +11210,22 @@
         <v>1398000</v>
       </c>
       <c r="C419" t="n">
-        <v>17471</v>
+        <v>34259</v>
       </c>
       <c r="D419" t="n">
-        <v>1502540</v>
+        <v>1501810</v>
       </c>
       <c r="E419" t="n">
-        <v>1494351</v>
+        <v>1492657</v>
       </c>
       <c r="F419" t="n">
-        <v>1407878</v>
+        <v>1406802</v>
       </c>
       <c r="G419" t="n">
-        <v>1468256</v>
+        <v>1467089</v>
       </c>
       <c r="H419" t="n">
-        <v>-0.1882011118820995</v>
+        <v>-0.1888463462979192</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11228,6 +11228,32 @@
         <v>-0.1888463462979192</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>1402000</v>
+      </c>
+      <c r="C420" t="n">
+        <v>29818</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1505612</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1478668</v>
+      </c>
+      <c r="F420" t="n">
+        <v>1403079</v>
+      </c>
+      <c r="G420" t="n">
+        <v>1462453</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-0.1914095911580216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -11259,25 +11259,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>1400000</v>
+        <v>1391000</v>
       </c>
       <c r="C421" t="n">
-        <v>2352</v>
+        <v>29740</v>
       </c>
       <c r="D421" t="n">
-        <v>1507685</v>
+        <v>1506305</v>
       </c>
       <c r="E421" t="n">
-        <v>1478450</v>
+        <v>1475700</v>
       </c>
       <c r="F421" t="n">
-        <v>1401317</v>
+        <v>1399381</v>
       </c>
       <c r="G421" t="n">
-        <v>1462484</v>
+        <v>1460462</v>
       </c>
       <c r="H421" t="n">
-        <v>-0.191392451254945</v>
+        <v>-0.1925104152556195</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11280,6 +11280,32 @@
         <v>-0.1925104152556195</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>1366000</v>
+      </c>
+      <c r="C422" t="n">
+        <v>38526</v>
+      </c>
+      <c r="D422" t="n">
+        <v>1506301</v>
+      </c>
+      <c r="E422" t="n">
+        <v>1471090</v>
+      </c>
+      <c r="F422" t="n">
+        <v>1389483</v>
+      </c>
+      <c r="G422" t="n">
+        <v>1455625</v>
+      </c>
+      <c r="H422" t="n">
+        <v>-0.1951847930356704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>-0.1951847930356704</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="C423" t="n">
+        <v>48538</v>
+      </c>
+      <c r="D423" t="n">
+        <v>1496953</v>
+      </c>
+      <c r="E423" t="n">
+        <v>1439786</v>
+      </c>
+      <c r="F423" t="n">
+        <v>1391229</v>
+      </c>
+      <c r="G423" t="n">
+        <v>1442656</v>
+      </c>
+      <c r="H423" t="n">
+        <v>-0.2023553544227861</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11332,6 +11332,32 @@
         <v>-0.2023553544227861</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>1385000</v>
+      </c>
+      <c r="C424" t="n">
+        <v>30651</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1495988</v>
+      </c>
+      <c r="E424" t="n">
+        <v>1437514</v>
+      </c>
+      <c r="F424" t="n">
+        <v>1388844</v>
+      </c>
+      <c r="G424" t="n">
+        <v>1440782</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-0.2033914892087723</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>-0.2033914892087723</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>1391000</v>
+      </c>
+      <c r="C425" t="n">
+        <v>48767</v>
+      </c>
+      <c r="D425" t="n">
+        <v>1492120</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1424316</v>
+      </c>
+      <c r="F425" t="n">
+        <v>1387381</v>
+      </c>
+      <c r="G425" t="n">
+        <v>1434606</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-0.2068062002217129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11337,25 +11337,25 @@
         <v>46294</v>
       </c>
       <c r="B424" t="n">
-        <v>1385000</v>
+        <v>1374339</v>
       </c>
       <c r="C424" t="n">
         <v>30651</v>
       </c>
       <c r="D424" t="n">
-        <v>1495988</v>
+        <v>1495813</v>
       </c>
       <c r="E424" t="n">
-        <v>1437514</v>
+        <v>1437071</v>
       </c>
       <c r="F424" t="n">
-        <v>1388844</v>
+        <v>1387001</v>
       </c>
       <c r="G424" t="n">
-        <v>1440782</v>
+        <v>1439962</v>
       </c>
       <c r="H424" t="n">
-        <v>-0.2033914892087723</v>
+        <v>-0.2038448672901537</v>
       </c>
     </row>
     <row r="425">
@@ -11363,25 +11363,77 @@
         <v>46295</v>
       </c>
       <c r="B425" t="n">
-        <v>1391000</v>
+        <v>1380293</v>
       </c>
       <c r="C425" t="n">
         <v>48767</v>
       </c>
       <c r="D425" t="n">
-        <v>1492120</v>
+        <v>1491632</v>
       </c>
       <c r="E425" t="n">
-        <v>1424316</v>
+        <v>1423105</v>
       </c>
       <c r="F425" t="n">
-        <v>1387381</v>
+        <v>1383054</v>
       </c>
       <c r="G425" t="n">
-        <v>1434606</v>
+        <v>1432597</v>
       </c>
       <c r="H425" t="n">
-        <v>-0.2068062002217129</v>
+        <v>-0.2079169765210973</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>1418000</v>
+      </c>
+      <c r="C426" t="n">
+        <v>55160</v>
+      </c>
+      <c r="D426" t="n">
+        <v>1489365</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1418826</v>
+      </c>
+      <c r="F426" t="n">
+        <v>1390685</v>
+      </c>
+      <c r="G426" t="n">
+        <v>1432959</v>
+      </c>
+      <c r="H426" t="n">
+        <v>-0.2077168266851704</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>1354000</v>
+      </c>
+      <c r="C427" t="n">
+        <v>49682</v>
+      </c>
+      <c r="D427" t="n">
+        <v>1485714</v>
+      </c>
+      <c r="E427" t="n">
+        <v>1410455</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1386941</v>
+      </c>
+      <c r="G427" t="n">
+        <v>1427703</v>
+      </c>
+      <c r="H427" t="n">
+        <v>-0.2106228696068051</v>
       </c>
     </row>
   </sheetData>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>-0.2106228696068051</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>1310000</v>
+      </c>
+      <c r="C428" t="n">
+        <v>83226</v>
+      </c>
+      <c r="D428" t="n">
+        <v>1478284</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1393927</v>
+      </c>
+      <c r="F428" t="n">
+        <v>1360632</v>
+      </c>
+      <c r="G428" t="n">
+        <v>1410948</v>
+      </c>
+      <c r="H428" t="n">
+        <v>-0.2198867107696646</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,32 @@
         <v>-0.2198867107696646</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>1277000</v>
+      </c>
+      <c r="C429" t="n">
+        <v>61625</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1468817</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1381620</v>
+      </c>
+      <c r="F429" t="n">
+        <v>1341956</v>
+      </c>
+      <c r="G429" t="n">
+        <v>1397464</v>
+      </c>
+      <c r="H429" t="n">
+        <v>-0.2273420157078918</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11488,6 +11488,32 @@
         <v>-0.2273420157078918</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>1219000</v>
+      </c>
+      <c r="C430" t="n">
+        <v>80485</v>
+      </c>
+      <c r="D430" t="n">
+        <v>1457744</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1363568</v>
+      </c>
+      <c r="F430" t="n">
+        <v>1306322</v>
+      </c>
+      <c r="G430" t="n">
+        <v>1375878</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-0.2392769172502066</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>-0.2392769172502066</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>1201000</v>
+      </c>
+      <c r="C431" t="n">
+        <v>60151</v>
+      </c>
+      <c r="D431" t="n">
+        <v>1435891</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1341440</v>
+      </c>
+      <c r="F431" t="n">
+        <v>1269041</v>
+      </c>
+      <c r="G431" t="n">
+        <v>1348791</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-0.2542533222384713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>-0.2542533222384713</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>1206000</v>
+      </c>
+      <c r="C432" t="n">
+        <v>61562</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1423365</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1331419</v>
+      </c>
+      <c r="F432" t="n">
+        <v>1245696</v>
+      </c>
+      <c r="G432" t="n">
+        <v>1333493</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-0.26271158795673</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>-0.26271158795673</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>1182000</v>
+      </c>
+      <c r="C433" t="n">
+        <v>54193</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1413618</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1318621</v>
+      </c>
+      <c r="F433" t="n">
+        <v>1218013</v>
+      </c>
+      <c r="G433" t="n">
+        <v>1316751</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-0.2719682414182993</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>-0.2719682414182993</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>1247000</v>
+      </c>
+      <c r="C434" t="n">
+        <v>136505</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1401398</v>
+      </c>
+      <c r="E434" t="n">
+        <v>1306106</v>
+      </c>
+      <c r="F434" t="n">
+        <v>1218832</v>
+      </c>
+      <c r="G434" t="n">
+        <v>1308778</v>
+      </c>
+      <c r="H434" t="n">
+        <v>-0.2763765139095843</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>-0.2763765139095843</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>1298000</v>
+      </c>
+      <c r="C435" t="n">
+        <v>165123</v>
+      </c>
+      <c r="D435" t="n">
+        <v>1392972</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1301775</v>
+      </c>
+      <c r="F435" t="n">
+        <v>1246179</v>
+      </c>
+      <c r="G435" t="n">
+        <v>1313642</v>
+      </c>
+      <c r="H435" t="n">
+        <v>-0.2736872078268539</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>-0.2736872078268539</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>1427000</v>
+      </c>
+      <c r="C436" t="n">
+        <v>149328</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1390860</v>
+      </c>
+      <c r="E436" t="n">
+        <v>1312416</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1298620</v>
+      </c>
+      <c r="G436" t="n">
+        <v>1333965</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-0.2624506191098861</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>-0.2624506191098861</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>1391000</v>
+      </c>
+      <c r="C437" t="n">
+        <v>91496</v>
+      </c>
+      <c r="D437" t="n">
+        <v>1385507</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1318057</v>
+      </c>
+      <c r="F437" t="n">
+        <v>1322343</v>
+      </c>
+      <c r="G437" t="n">
+        <v>1341969</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-0.2580252067155246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>-0.2580252067155246</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>1417000</v>
+      </c>
+      <c r="C438" t="n">
+        <v>115976</v>
+      </c>
+      <c r="D438" t="n">
+        <v>1383811</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1324651</v>
+      </c>
+      <c r="F438" t="n">
+        <v>1350567</v>
+      </c>
+      <c r="G438" t="n">
+        <v>1353010</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-0.2519206367197543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>-0.2519206367197543</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>1361000</v>
+      </c>
+      <c r="C439" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D439" t="n">
+        <v>1383059</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1325194</v>
+      </c>
+      <c r="F439" t="n">
+        <v>1375554</v>
+      </c>
+      <c r="G439" t="n">
+        <v>1361269</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.2473542348000851</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>-0.2473542348000851</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>1466000</v>
+      </c>
+      <c r="C440" t="n">
+        <v>114349</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1387013</v>
+      </c>
+      <c r="E440" t="n">
+        <v>1334997</v>
+      </c>
+      <c r="F440" t="n">
+        <v>1417915</v>
+      </c>
+      <c r="G440" t="n">
+        <v>1379975</v>
+      </c>
+      <c r="H440" t="n">
+        <v>-0.2370116855435975</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>-0.2370116855435975</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>1452000</v>
+      </c>
+      <c r="C441" t="n">
+        <v>33241</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1377939</v>
+      </c>
+      <c r="E441" t="n">
+        <v>1337563</v>
+      </c>
+      <c r="F441" t="n">
+        <v>1417395</v>
+      </c>
+      <c r="G441" t="n">
+        <v>1377633</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-0.2383065775760307</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>-0.2383065775760307</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>1374000</v>
+      </c>
+      <c r="C442" t="n">
+        <v>89537</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1375084</v>
+      </c>
+      <c r="E442" t="n">
+        <v>1339596</v>
+      </c>
+      <c r="F442" t="n">
+        <v>1413963</v>
+      </c>
+      <c r="G442" t="n">
+        <v>1376214</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-0.2390911428168602</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>-0.2390911428168602</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>1372000</v>
+      </c>
+      <c r="C443" t="n">
+        <v>48969</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1369690</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1338758</v>
+      </c>
+      <c r="F443" t="n">
+        <v>1407303</v>
+      </c>
+      <c r="G443" t="n">
+        <v>1371917</v>
+      </c>
+      <c r="H443" t="n">
+        <v>-0.2414669545433183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>-0.2414669545433183</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>1366000</v>
+      </c>
+      <c r="C444" t="n">
+        <v>41310</v>
+      </c>
+      <c r="D444" t="n">
+        <v>1369625</v>
+      </c>
+      <c r="E444" t="n">
+        <v>1338780</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1412742</v>
+      </c>
+      <c r="G444" t="n">
+        <v>1373716</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-0.2404722872647755</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/삼성바이오로직스_일별_기준주가.xlsx
+++ b/data/삼성바이오로직스_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>-0.2404722872647755</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>1487000</v>
+      </c>
+      <c r="C445" t="n">
+        <v>99012</v>
+      </c>
+      <c r="D445" t="n">
+        <v>1374361</v>
+      </c>
+      <c r="E445" t="n">
+        <v>1346372</v>
+      </c>
+      <c r="F445" t="n">
+        <v>1416788</v>
+      </c>
+      <c r="G445" t="n">
+        <v>1379174</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-0.2374545585230933</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
